--- a/Data/Importance_Scores.xlsx
+++ b/Data/Importance_Scores.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nationalgridplc-my.sharepoint.com/personal/robert_everitt_uk_nationalgrid_com/Documents/Data Engineering Course/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFC5310F-46C0-46EC-90BA-11EA59A5354C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{18B9EEB7-2C58-462E-9AE4-FC6D38674ACA}"/>
   </bookViews>
